--- a/data/trans_orig/Q23_tabaco-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media de inicio en el consumo de tabaco</t>
+          <t>Edad media de inicio en el consumo de tabaco (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 16,13</t>
+          <t>15,59; 16,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 16,26</t>
+          <t>15,69; 16,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,71; 16,63</t>
+          <t>15,73; 16,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,22; 15,89</t>
+          <t>15,2; 15,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,97; 19,96</t>
+          <t>17,91; 19,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,78; 19,32</t>
+          <t>17,78; 19,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 19,85</t>
+          <t>17,71; 19,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,17; 18,49</t>
+          <t>17,17; 18,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,96</t>
+          <t>16,31; 16,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,0</t>
+          <t>16,35; 16,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,42; 17,38</t>
+          <t>16,44; 17,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 16,48</t>
+          <t>15,87; 16,51</t>
         </is>
       </c>
     </row>
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,73</t>
+          <t>16,28; 16,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 16,78</t>
+          <t>16,44; 16,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,76</t>
+          <t>16,32; 16,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,27; 16,82</t>
+          <t>16,25; 16,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,21</t>
+          <t>16,72; 17,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,13; 17,79</t>
+          <t>17,12; 17,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 17,93</t>
+          <t>17,29; 17,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 17,49</t>
+          <t>17,02; 17,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 16,82</t>
+          <t>16,51; 16,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,16</t>
+          <t>16,79; 17,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 17,02</t>
+          <t>16,51; 17,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,66</t>
+          <t>16,9; 17,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 18,12</t>
+          <t>17,13; 18,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,59</t>
+          <t>16,68; 17,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 18,45</t>
+          <t>17,52; 18,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,56; 19,06</t>
+          <t>17,62; 19,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 18,59</t>
+          <t>17,28; 18,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,73</t>
+          <t>16,83; 17,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,56; 18,52</t>
+          <t>17,57; 18,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 18,02</t>
+          <t>17,28; 18,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 18,1</t>
+          <t>17,33; 18,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 17,51</t>
+          <t>16,86; 17,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,43</t>
+          <t>17,67; 18,32</t>
         </is>
       </c>
     </row>
@@ -1136,52 +1136,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,53</t>
+          <t>16,22; 16,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 16,66</t>
+          <t>16,35; 16,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,68</t>
+          <t>16,34; 16,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,76</t>
+          <t>16,32; 16,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,25; 17,81</t>
+          <t>17,22; 17,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,99</t>
+          <t>17,42; 18,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,97</t>
+          <t>17,43; 17,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 17,68</t>
+          <t>17,27; 17,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,94</t>
+          <t>16,65; 16,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,12</t>
+          <t>16,83; 17,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,05</t>
+          <t>16,67; 17,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,53</t>
+          <t>15,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,76</t>
+          <t>17,81</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,16</t>
+          <t>16,19</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,59; 16,15</t>
+          <t>15,62; 16,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 16,28</t>
+          <t>15,7; 16,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 16,6</t>
+          <t>15,73; 16,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,2; 15,89</t>
+          <t>15,24; 15,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,91; 19,74</t>
+          <t>17,94; 19,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,78; 19,28</t>
+          <t>17,74; 19,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 19,7</t>
+          <t>17,71; 20,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,17; 18,44</t>
+          <t>17,21; 18,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,95</t>
+          <t>16,31; 16,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,35; 16,97</t>
+          <t>16,37; 16,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 17,32</t>
+          <t>16,43; 17,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,87; 16,51</t>
+          <t>15,88; 16,49</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,56</t>
+          <t>16,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,24</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,81</t>
+          <t>17,0</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 16,7</t>
+          <t>16,29; 16,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 16,81</t>
+          <t>16,45; 16,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,74</t>
+          <t>16,32; 16,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,25; 16,83</t>
+          <t>16,57; 17,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 17,24</t>
+          <t>16,69; 17,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 17,8</t>
+          <t>17,12; 17,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 17,91</t>
+          <t>17,29; 17,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 17,54</t>
+          <t>17,07; 17,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 16,82</t>
+          <t>16,5; 16,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 17,14</t>
+          <t>16,79; 17,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,15</t>
+          <t>16,8; 17,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 17,01</t>
+          <t>16,84; 17,19</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,94</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>18,12</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,98</t>
+          <t>18,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 17,64</t>
+          <t>16,89; 17,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 18,1</t>
+          <t>17,1; 18,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,61</t>
+          <t>16,72; 17,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 18,54</t>
+          <t>17,5; 18,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,62; 19,04</t>
+          <t>17,57; 19,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,28; 18,53</t>
+          <t>17,32; 18,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,72</t>
+          <t>16,84; 17,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,5</t>
+          <t>17,69; 18,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,28; 18,04</t>
+          <t>17,29; 18,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,33; 18,11</t>
+          <t>17,31; 18,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,52</t>
+          <t>16,88; 17,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 18,32</t>
+          <t>17,67; 18,34</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,57</t>
+          <t>16,71</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,45</t>
+          <t>17,53</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>17,04</t>
         </is>
       </c>
     </row>
@@ -1146,52 +1146,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 16,7</t>
+          <t>16,3; 16,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,77</t>
+          <t>16,54; 16,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,8</t>
+          <t>17,26; 17,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 18,0</t>
+          <t>17,42; 17,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,93</t>
+          <t>17,42; 17,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,27; 17,68</t>
+          <t>17,34; 17,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,93</t>
+          <t>16,66; 16,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,13</t>
+          <t>16,83; 17,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,14</t>
+          <t>16,82; 17,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,67; 17,05</t>
+          <t>16,92; 17,19</t>
         </is>
       </c>
     </row>
